--- a/www/download/COUNTRY.DEU.EXI382.xlsx
+++ b/www/download/COUNTRY.DEU.EXI382.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>Alemanha</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -967,2643 +972,4879 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1268773006135</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1268773006135</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1268773006135</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1268773006135</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1268773006135</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1268773006135</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1268773006135</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1268773006135</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1268773006135</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1268773006135</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1268773006135</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1268773006135</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1267981595092</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1267981595092</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1267981595092</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1267981595092</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1267981595092</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1267981595092</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1267981595092</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1267981595092</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1267981595092</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1267981595092</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1267981595092</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1267981595092</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1267981595092</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1267981595092</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1267981595092</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>51.285</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>37.958</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>37.969</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>37.947</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>38.407</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>39.031</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>39.917</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>39.809</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>39.63</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>39.2</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>38.898</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>39.326</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>39.635</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>40.325</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>40.856</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>40.892</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>41.02</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>41.57</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>42.033</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>42.771</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>44.554</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>44.286</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>44.993</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>48.032</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>46.997</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>47.887</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>49.945</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>45.393</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>34.161</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>34.115</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>34.036</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>34.447</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>35.046</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>35.922</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>35.797</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>35.57</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>35.078</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>34.701</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>34.916</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>35.152</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>35.798</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>36.353</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>36.407</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>36.533</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>37.024</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>37.489</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>38.166</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>39.727</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>39.44</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>40.034</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>42.763</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>41.733</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>42.439</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>44.347</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>66615.956</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>58083.9</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>57352.2</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>56907.1</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>57362.9</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>57716.9</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>57960</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>57401.1</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>56704.2</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>55851</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>55386.9</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>55500.1</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>56465</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>57439.1</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>57950</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>56133.9</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>57013.1</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>57914.1</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>57763</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>58439.835</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>60568.02</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>60132.111</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>60811.469</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>64373.414</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>63003.347</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>63897.953</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>65968.562</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>55896.049</t>
+          <t>114602258087.009</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>40558.5</t>
+          <t>105330437117.236</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>39737.8</t>
+          <t>102012011003.399</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>38989.1</t>
+          <t>103330403783.63</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>39157.1</t>
+          <t>107261880115.45</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>39314.9</t>
+          <t>110228897890.693</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>48835.9</t>
+          <t>108393856770.938</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>39442.9</t>
+          <t>101773005082.813</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>47084.195</t>
+          <t>107204844768.821</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>46975.9</t>
+          <t>112240900159.69</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>46377.1</t>
+          <t>113351597932</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>42942.6</t>
+          <t>118155906616.473</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>47232</t>
+          <t>120333238377.793</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>48199</t>
+          <t>127965007992.268</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>48697</t>
+          <t>109143443957.188</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>46934.8</t>
+          <t>116061097708.19</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>47845.2</t>
+          <t>121161343798.66</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>48702</t>
+          <t>126016349221.161</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>48736</t>
+          <t>128272023115.004</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>49393.718</t>
+          <t>114823537046.642</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>51172.842</t>
+          <t>114883194617.247</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>50768.709</t>
+          <t>117566987358.703</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>51327.958</t>
+          <t>112317986383.31</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>54426.214</t>
+          <t>121480820711.18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>53168.715</t>
+          <t>116072230785.376</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>53749.309</t>
+          <t>125427933052.688</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>55620.992</t>
+          <t>134870931084.26</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>55757332973.6843</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>53333180941.8206</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>49633456810.623</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>49152812210.2428</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>50176303569.1104</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>50675036334.7015</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>46016630011.2001</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>44234504527.9877</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>55516716440.5853</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>48112099016.0297</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>46066979706.2166</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>47333080228.5932</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>42193047493.1759</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>45148129979.7592</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>44095328422.0827</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>45334015603.1312</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>43046667115.204</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>42551530258.3838</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>43974302957.3872</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>44861799512.0023</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>38634907256.1261</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>42706392734.1503</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>44905255492.7247</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>45984120798.6186</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>43557536660.2806</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>51767331313.4706</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>49515983408.9928</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>10798891.9572277</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>6458334.5889173</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>5802519.42973616</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>5768674.92699723</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>6148857.55913144</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>5646654.27524849</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>5173591.85920142</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>5144253.81201893</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>5294782.16410054</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>6121296.23337906</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>5889899.2718598</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>4988236.25097148</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>4737799.25497074</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>4645014.02825064</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>5054645.56320188</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>4811353.82449396</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>4614483.64743894</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>4005856.12608867</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>4527401.438352</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>81551883.5352754</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>17042397.1624271</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>37901767.3052288</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>23428570.347597</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>4013910.48043949</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>6775830.96326244</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>26676532.3676773</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>4490783.6341048</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>125593.190127835</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>244497.875701525</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>263791.733066464</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>267200.318619973</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>282547.666944562</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>338991.881907838</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>338145.896269848</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>322283.786924605</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>291874.767869375</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>280095.536291628</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>300007.797029213</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>315721.551370071</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>331035.455945603</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>337284.118420518</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>341995.878235792</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>379590.228242917</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>403276.304005627</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>455042.620841563</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>445993.539878296</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>474737.686430137</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>544980.107731001</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>478975.879844598</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>513120.934007349</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>536921.795896962</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>560247.083807312</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>538125.775877725</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>541273.103236474</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>427191.679971183</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>800413.620698197</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>844315.060481956</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>879232.311458719</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>962706.999825804</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>1182625.28441804</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1167700.08117373</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>1062778.5189305</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>1028392.65710373</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>1052193.54001609</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>1139157.68972887</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>1270212.61280787</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>1340261.0376936</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>1432121.60628257</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>1224059.99750177</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>1501059.92801209</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>1631353.98612729</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>1872772.96005428</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>1862122.29776614</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>1725365.89188242</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>1950044.24922043</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>1818930.3287774</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>1837195.48477761</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>1932572.13272898</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>1967409.30789353</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>2022457.31552659</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>2135095.87561636</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>0.00248784564534521</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>-0.239525952066432</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>-0.199374725165228</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>-0.206777837385267</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-0.219609711862238</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-0.224176185284961</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>0.0612663288922719</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>-0.108322780578426</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>-0.151891577149474</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>-0.023615660909698</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>0.00673194326541093</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>-0.0927571205465965</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>0.119426133123866</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>0.0675746707914178</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>0.104357349011076</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>0.0353108890878457</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>0.111472808613565</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>0.144541681680272</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>0.108283627536307</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>0.101019552301999</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>0.324523477450642</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>0.188784765022938</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>0.143027856397897</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>0.1835871302445</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>0.220654761196289</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>0.0382862554247423</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>0.123293688319837</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1228.31671329386</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>1561.230085238</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>1454.88661323832</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>1444.14185598316</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>1456.62332188938</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>1445.95777933924</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1281.0152555874</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>1235.70423577309</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>1560.7735856225</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>1371.57474816168</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>1327.54040823615</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>1355.62722615997</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>1200.30289864539</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>1261.19140677571</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>1212.97632718349</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>1245.20052745682</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>1178.29543468121</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>1149.29586912227</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>1172.99215656287</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>1175.43479771674</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>972.519681414612</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>1082.82759399365</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>1121.67601739572</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>1075.33172658195</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>1043.72897414838</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>1219.79724486979</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>1116.56418605065</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.137</t>
+          <t>62839592136.403</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.123</t>
+          <t>54166744523.7989</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.117</t>
+          <t>49194868868.3759</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1.137</t>
+          <t>50801745407.9158</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1.171</t>
+          <t>51881313335.5375</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1.217</t>
+          <t>52208374105.1686</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.185</t>
+          <t>56309460564.1888</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.229</t>
+          <t>63674720195.9096</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>1.378</t>
+          <t>65604775528.8825</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>76265049635.3757</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>73556557014.7858</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>1.282</t>
+          <t>75835592186.7682</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>1.317</t>
+          <t>70592573854.5692</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>1.371</t>
+          <t>74703465429.3338</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>1.363</t>
+          <t>66984460175.0215</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1.405</t>
+          <t>70024066406.0262</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>1.463</t>
+          <t>68218009457.7175</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>68163576840.3651</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>1.528</t>
+          <t>71711411030.9166</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>1.591</t>
+          <t>70763943365.7426</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>1.605</t>
+          <t>68970636103.5884</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>79186861626.3982</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>73091422893.5679</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>1.832</t>
+          <t>75992766939.0104</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>70951040126.9472</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>1.883</t>
+          <t>78913374702.8164</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>1.886</t>
+          <t>81074018470.8596</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>88210032294.3536</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>59556738436.2984</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>55227231877.0559</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>57509753484.7331</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>60121223172.1207</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>60117713908.6722</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>63700502450.6364</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>68212347841.2827</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>70530152696.2317</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>79884576709.5454</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>77382915990.6243</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>77426796328.2067</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>72453154989.9627</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>77706526586.9645</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>69147263125.1506</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>72001850450.4541</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>69938510764.4862</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>69401820267.1413</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>73371480260.086</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>71620803785.4544</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>69368626815.4719</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>80272755607.208</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>80263208744.7103</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>84695113234.6417</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>79269117611.6246</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>88086109810.6462</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>88379518997.3137</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>-25370440157.9506</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>-5389993912.4995</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>-6032363008.67997</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>-6708008076.81728</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-8239909836.58319</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-7909339803.50363</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>-7391041886.44761</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>-4537627645.37313</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>-4925377167.34916</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>-3619527074.16964</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>-3826358975.83844</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>-1591204141.43845</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>-1860581135.39356</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>-3003061157.63072</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>-2162802950.12916</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>-1977784044.42788</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>-1720501306.76873</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>-1238243426.77622</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>-1660069229.1694</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>-856860419.711725</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>-397990711.883513</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>-1085893980.80981</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>-7171785851.14238</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>-8702346295.6313</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>-8318077484.67737</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>-9172735107.82986</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>-7305500526.45409</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>3.301</t>
+          <t>1231.37257568014</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>3.287</t>
+          <t>1187.27496267661</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>3.338</t>
+          <t>1164.81899457736</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>1145.52532612542</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>1136.73469387744</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>3.833</t>
+          <t>1121.80848028386</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>3.981</t>
+          <t>1359.49835755224</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>3.889</t>
+          <t>1101.84931698161</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>3.922</t>
+          <t>1323.70522412906</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>4.043</t>
+          <t>1339.18410399679</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>4.158</t>
+          <t>1336.47733494694</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>4.475</t>
+          <t>1229.8831481268</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>4.726</t>
+          <t>1343.65043240797</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>4.828</t>
+          <t>1346.41600089354</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>4.454</t>
+          <t>1339.55932110155</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>4.753</t>
+          <t>1289.16966517397</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>5.029</t>
+          <t>1309.64333616167</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>5.206</t>
+          <t>1315.41702679339</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>5.273</t>
+          <t>1300.00800234714</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>5.517</t>
+          <t>1294.17669474227</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>5.638</t>
+          <t>1288.12515031647</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>5.829</t>
+          <t>1287.24894688609</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>6.211</t>
+          <t>1282.10693373676</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>6.234</t>
+          <t>1272.74879232599</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>6.411</t>
+          <t>1274.03274169274</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>6.636</t>
+          <t>1266.49871375327</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>6.703</t>
+          <t>1254.22950279467</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1.137</t>
+          <t>1298.9350426468</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1.123</t>
+          <t>1530.21497444519</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.117</t>
+          <t>1510.50067160086</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1.137</t>
+          <t>1499.64687590583</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1.171</t>
+          <t>1493.55325852056</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>1.217</t>
+          <t>1478.74510004957</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.185</t>
+          <t>1452.01292682298</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.229</t>
+          <t>1441.91263282153</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>1.378</t>
+          <t>1430.84027252108</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1424.77040816323</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1423.90097177216</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>1.282</t>
+          <t>1411.28261201243</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>1.317</t>
+          <t>1424.62470039129</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>1.371</t>
+          <t>1424.40421574684</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>1.363</t>
+          <t>1418.39631877833</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1.405</t>
+          <t>1372.73549838574</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>1.463</t>
+          <t>1389.88542174533</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1393.17055568908</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>1.528</t>
+          <t>1374.22977184575</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>1.591</t>
+          <t>1366.34597655239</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>1.605</t>
+          <t>1359.42944970778</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1357.81601369358</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1351.58337159336</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>1.832</t>
+          <t>1340.23151870058</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1340.58272056562</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>1.883</t>
+          <t>1334.34996564965</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>1.886</t>
+          <t>1320.83173295054</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>419381.76245425</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>453097.443629414</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>515562.957546048</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>549248.844647628</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>587123.719218108</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>705470.059711132</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>760673.910219076</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>788125.823943253</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>776552.986054649</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>851727.997298421</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>920599.312902699</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>1038013.30073979</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>1125921.5713072</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>1133482.22835223</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>964613.634234606</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>1134061.17348495</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>1249245.09746308</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>1349454.58981987</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>1347590.39345997</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>1409375.32684079</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>1550338.35181893</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>1579585.25589871</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>1678657.76597094</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>1720643.93667182</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>1756232.84701048</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>1797221.75130696</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>1881289.00552181</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>18940361193.81</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>18136282906.0454</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>19046249748.4327</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>19989551806.3788</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>21180811829.8168</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>23632940395.4492</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>24249610398.6703</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>24396060627.3298</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>25381885785.2782</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>28364399799.0967</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>29638987209.1616</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>32024172880.9492</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>32442427325.8817</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>36012244936.44</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>28136610072.5958</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>31741866795.3883</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>34392053991.7393</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>37689362555.6355</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>37080523033.2692</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>33092543102.7139</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>34934324849.4641</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>35946126869.3682</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>34311397643.277</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>39162811873.2809</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>37041897196.0002</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>39026072232.8403</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>42987482092.5999</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>408862.470603485</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>434717.58947785</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>488062.040916488</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>517148.532656115</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>572243.157539386</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>700809.423385999</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>714490.689671423</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>666502.187999492</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>667626.702746574</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>698100.327089537</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>765007.817600642</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>869198.725427782</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>904842.452177907</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>932004.642101613</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>804952.404590047</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>957720.329766041</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>1076554.10439838</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>1130394.53868087</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>1135894.2732006</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>1156287.2579096</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>1249817.17239463</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>1277319.96475509</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>1380332.78858566</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>1450714.52597338</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>1494729.05304976</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>1549340.72870065</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>1640734.01861425</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>66615.956</t>
+          <t>75820498473.7089</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>58083.9</t>
+          <t>68569379719.9562</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>57352.2</t>
+          <t>63093284812.3817</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>56907.1</t>
+          <t>64743652346.7168</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>57362.9</t>
+          <t>70332377003.1218</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>57716.9</t>
+          <t>75118260685.5132</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>57960</t>
+          <t>73110687864.576</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>57401.1</t>
+          <t>67719065965.8806</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>56704.2</t>
+          <t>72482519509.8822</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>55851</t>
+          <t>76455695321.8558</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>55386.9</t>
+          <t>77172775719.9667</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>55500.1</t>
+          <t>82741557490.7879</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>56465</t>
+          <t>75580864688.7826</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>57439.1</t>
+          <t>83105353017.8055</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>57950</t>
+          <t>71620308736.3985</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>56133.9</t>
+          <t>80022751599.8853</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>57013.1</t>
+          <t>82696071149.4884</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>57914.1</t>
+          <t>81968552238.0158</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>57763</t>
+          <t>84541390526.0059</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>58439.835</t>
+          <t>76951682791.4938</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>60568.02</t>
+          <t>74855116184.1051</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>60132.111</t>
+          <t>83075780051.3854</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>60811.469</t>
+          <t>78667336226.252</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>64373.414</t>
+          <t>88327374000.4089</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>63003.347</t>
+          <t>84126164363.4787</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>63897.953</t>
+          <t>93884743705.8191</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>65968.562</t>
+          <t>100623007616.439</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>55896.049</t>
+          <t>10519.2918507656</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>40558.5</t>
+          <t>18379.8541515642</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>39737.8</t>
+          <t>27500.9166295592</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>38989.1</t>
+          <t>32100.3119915131</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>39157.1</t>
+          <t>14880.5616787215</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>39314.9</t>
+          <t>4660.63632513366</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>48835.9</t>
+          <t>46183.2205476533</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>39442.9</t>
+          <t>121623.635943761</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>47084.195</t>
+          <t>108926.283308075</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>46975.9</t>
+          <t>153627.670208884</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>46377.1</t>
+          <t>155591.495302056</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>42942.6</t>
+          <t>168814.575312008</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>47232</t>
+          <t>221079.11912929</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>48199</t>
+          <t>201477.58625062</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>48697</t>
+          <t>159661.229644559</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>46934.8</t>
+          <t>176340.843718906</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>47845.2</t>
+          <t>172690.9930647</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>48702</t>
+          <t>219060.051138994</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>48736</t>
+          <t>211696.120259373</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>49393.718</t>
+          <t>253088.06893119</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>51172.842</t>
+          <t>300521.179424305</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>50768.709</t>
+          <t>302265.291143622</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>51327.958</t>
+          <t>298324.977385278</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>54426.214</t>
+          <t>269929.410698431</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>53168.715</t>
+          <t>261503.793960712</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>53749.309</t>
+          <t>247881.022606304</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>55620.992</t>
+          <t>240554.986907556</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>79180.408</t>
+          <t>-56880137279.8988</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>76651.164</t>
+          <t>-50433096813.9108</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>75134.759</t>
+          <t>-44047035063.949</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>75613.205</t>
+          <t>-44754100540.3379</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>77900.571</t>
+          <t>-49151565173.305</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>79594.657</t>
+          <t>-51485320290.064</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>78419.658</t>
+          <t>-48861077465.9057</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>73964.452</t>
+          <t>-43323005338.5509</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>77367.348</t>
+          <t>-47100633724.604</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>80535.69</t>
+          <t>-48091295522.7591</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>81495.698</t>
+          <t>-47533788510.8051</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>84292.076</t>
+          <t>-50717384609.8387</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>85817.791</t>
+          <t>-43138437362.9009</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>90923.818</t>
+          <t>-47093108081.3655</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>79360.168</t>
+          <t>-43483698663.8026</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>83258.169</t>
+          <t>-48280884804.4969</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>86029.768</t>
+          <t>-48304017157.7492</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>89732.343</t>
+          <t>-44279189682.3804</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>91339.618</t>
+          <t>-47460867492.7367</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>82635.638</t>
+          <t>-43859139688.78</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>82385.581</t>
+          <t>-39920791334.641</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>84126.979</t>
+          <t>-47129653182.0172</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>81677.002</t>
+          <t>-44355938582.975</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>87678.674</t>
+          <t>-49164562127.128</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>84218.732</t>
+          <t>-47084267167.4785</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>90549.15</t>
+          <t>-54858671472.9788</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>96417.946</t>
+          <t>-57635525523.8393</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.257</t>
+          <t>841189.809199562</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.497</t>
+          <t>828052.867528844</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.533</t>
+          <t>832345.325558004</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.557</t>
+          <t>839238.513954737</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.606</t>
+          <t>870461.198613323</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.741</t>
+          <t>896746.670325205</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.734</t>
+          <t>826838.151212323</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.672</t>
+          <t>871995.046252464</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.647</t>
+          <t>910316.503199755</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.661</t>
+          <t>909917.074386135</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.715</t>
+          <t>891559.691629188</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.792</t>
+          <t>930239.197013306</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.833</t>
+          <t>953035.328443424</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.894</t>
+          <t>960236.768491516</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.777</t>
+          <t>942413.763540608</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>0.938</t>
+          <t>962867.918751155</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>1.011</t>
+          <t>999918.757622402</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>1.163</t>
+          <t>1017043.94457679</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>1.151</t>
+          <t>1064785.36472542</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1105599.2474157</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>1.191</t>
+          <t>1097704.5149491</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>1.104</t>
+          <t>1125211.97433097</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>1.124</t>
+          <t>1211700.68628875</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>1.173</t>
+          <t>1231811.17508602</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>1.192</t>
+          <t>1253082.84182499</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>1.221</t>
+          <t>1293110.17109894</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>1.275</t>
+          <t>1278745.91327114</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>33692.752</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>32174.7</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>31871.9</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>31402.3</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>31480.6</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>31596.4</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>31389</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>30862.3</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>30426.5</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>29878.7</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>29852.2</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>29368.6</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>29721.5</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>30137.5</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>30494.1</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>29349.7</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>29951.5</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>30619.2</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>30722.2</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>31593.913</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>32106.48</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>30958.718</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>31369.939</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>33750.72</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>33053.177</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>33373.265</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>34191.442</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>1276881.61016686</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.209</t>
+          <t>1260925.13296489</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.226</t>
+          <t>1253887.92200283</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.231</t>
+          <t>1276707.78587048</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.245</t>
+          <t>1314885.93780704</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.294</t>
+          <t>1366459.67760715</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.294</t>
+          <t>1330617.66616972</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>1379517.92305336</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.255</t>
+          <t>1546598.54184584</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.245</t>
+          <t>1425531.9658001</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.262</t>
+          <t>1403145.40281526</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.276</t>
+          <t>1438491.01000578</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.288</t>
+          <t>1477941.99173003</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.296</t>
+          <t>1538641.27649132</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>1530039.80652916</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>0.331</t>
+          <t>1577381.45250843</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>0.352</t>
+          <t>1642062.99909761</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>0.397</t>
+          <t>1672633.44107859</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>0.387</t>
+          <t>1714651.38131562</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>0.409</t>
+          <t>1785336.44090186</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>0.464</t>
+          <t>1801548.90083513</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>0.406</t>
+          <t>1851836.94279276</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>0.432</t>
+          <t>1964196.34351389</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>0.451</t>
+          <t>2055701.41997646</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>0.468</t>
+          <t>2064724.67263133</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>2112840.45636819</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>0.452</t>
+          <t>2115963.78567541</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>49368.581</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>48178.39</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>45492.746</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>44765.368</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>45426.647</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>46044.57</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>41821.133</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>40350.635</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>51302.498</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>43904.049</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>42608.405</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>43541.586</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>39093.306</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>41518.779</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>40963.15</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>42026.291</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>39668.762</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>39031.491</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>40298.963</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>41632.614</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>36148.869</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>39851.946</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>41976.602</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>43128.102</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>40944.263</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>48112.064</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>45923.821</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>13.22</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>-15.82</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>-12.65</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>-12.9</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>-13.8</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>-14.62</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>16.77</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>-2.25</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>-8.22</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>8.84</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>-1.38</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>20.82</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>16.09</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>18.88</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>11.68</t>
-        </is>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>20.61</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>24.78</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>20.94</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>18.64</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>41.56</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>27.39</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>22.28</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>26.2</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>29.86</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>11.72</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>21.12</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>9.838</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>6.126</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>5.586</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>5.522</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>5.806</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>5.336</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>4.877</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>4.83</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>4.972</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>5.645</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>5.482</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>4.628</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>4.427</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>4.361</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>4.752</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>4.448</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>4.256</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>3.725</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>4.176</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>91.413</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>18.314</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>41.941</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>26.013</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>3.911</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>7.087</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>29.648</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>4.401</t>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>850930.920803539</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>853175.99146659</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>836973.113375706</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>866528.245656883</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>883627.849627587</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>885722.500535486</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>989406.037567788</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>967281.570287239</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>803007.484438691</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>1001017.10613395</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>1046680.96999141</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>1103006.64902154</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>1170255.19131586</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>1196761.11080331</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>1093139.32876594</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>1183970.24250718</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>1260050.82427174</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>1291281.32009481</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>1308549.45593787</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>1358882.1441929</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>1449554.63695353</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>1514923.97112214</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>1538721.70491469</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>1542930.20186637</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>1646363.32297067</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>1639903.76935098</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>1691760.3415991</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>55896048611.7189</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>40558499999.9997</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>39737800000.0048</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>38989100000.0047</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>39157099999.9859</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>39314900000.0114</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>48835899999.9803</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>39442900000.0071</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>47084194822.2647</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>46975900000.0133</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>46377100000.0077</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>42942599999.9878</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>47231999999.9976</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>48198999999.9895</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>48696999999.984</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>46934800000</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>47845199999.9889</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>48701999999.9996</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>48735999999.9936</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>49393718414.1668</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>51172841709.8672</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>50768709051.4442</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>51327957926.849</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>54426213572.8534</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>53168714510.3535</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>53749308582.7953</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>55620991634.2714</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>66615956342.1206</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>58083899999.9965</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>57352200000.0111</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>56907099999.9991</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>57362899999.9863</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>57716900000.0125</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>57959999999.9807</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>57401100000.0125</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>56704200000.0026</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>55851000000.0131</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>55386900000.0068</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>55500099999.9919</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>56465000000.0007</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>57439099999.993</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>57949999999.9866</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>56133900000.0017</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>57013099999.9871</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>57914099999.9958</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>57762999999.9933</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>58439835150.6908</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>60568019866.4359</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>60132110634.2479</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>60811468542.7504</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>64373414211.2917</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>63003347070.457</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>63897952780.7039</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>65968561950.3728</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>33692751670.5659</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>32174699999.9988</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>31871900000.0083</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>31402299999.996</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>31480599999.9911</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>31596400000.0056</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>31388999999.9933</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>30862299999.9975</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>30426500000.0052</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>29878700000.0043</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>29852199999.9967</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>29368599999.9849</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>29721499999.995</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>30137500000.0039</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>30494099999.999</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>29349699999.9991</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>29951499999.9922</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>30619199999.9939</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>30722199999.9895</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>31593913257.3062</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>32106479534.5123</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>30958718055.2778</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>31369938885.8476</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>33750719737.0059</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>33053177367.6225</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>33373264925.0711</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>34191442285.1365</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>51285055.9535133</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>37958000.0000038</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>37968999.9999987</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>37947000.0000004</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>38406999.9999913</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>39030999.9999851</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>39916999.9999916</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>39809000.000014</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>39629999.9999945</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>39200000.0000103</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>38898000.0000094</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>39325999.9999935</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>39634999.9999943</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>40325000.0000013</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>40855999.9999853</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>40892000.0000089</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>41019999.9999955</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>41570000.0000004</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>42033000.0000005</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>42770891.2336743</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>44554000.1207533</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>44285904.7380612</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>44992761.6903577</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>48031562.6912767</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>46996985.7912794</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>47886952.0183142</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>49944713.0960498</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>45393286.9025001</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>34161000.0000034</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>34114999.9999985</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>34035999.9999999</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>34446999.999991</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>35045999.9999851</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>35921999.9999918</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>35797000.0000149</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>35569999.9999954</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>35078000.0000105</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>34701000.0000104</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>34915999.9999939</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>35151999.9999944</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>35798000.0000018</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>36352999.9999846</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>36407000.0000087</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>36532999.999996</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>37024000.0000007</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>37489000.0000014</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>38166131.885108</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>39726607.0748598</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>39439697.4837352</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>40034069.3714614</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>42762730.4783276</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>41732612.3343668</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>42439291.8832972</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>44346741.5734814</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>66615956342.1206</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>58083899999.9965</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>57352200000.0111</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>56907099999.9991</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>57362899999.9863</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>57716900000.0125</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>57959999999.9807</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>57401100000.0125</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>56704200000.0026</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>55851000000.0131</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>55386900000.0068</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>55500099999.9919</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>56465000000.0007</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>57439099999.993</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>57949999999.9866</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>56133900000.0017</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>57013099999.9871</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>57914099999.9958</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>57762999999.9933</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>58439835150.6908</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>60568019866.4359</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>60132110634.2479</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>60811468542.7504</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>64373414211.2917</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>63003347070.457</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>63897952780.7039</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>65968561950.3728</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>55896048611.7189</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>40558499999.9997</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>39737800000.0048</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>38989100000.0047</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>39157099999.9859</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>39314900000.0114</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>48835899999.9803</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>39442900000.0071</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>47084194822.2647</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>46975900000.0133</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>46377100000.0077</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>42942599999.9878</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>47231999999.9976</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>48198999999.9895</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>48696999999.984</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>46934800000</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>47845199999.9889</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>48701999999.9996</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>48735999999.9936</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>49393718414.1668</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>51172841709.8672</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>50768709051.4442</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>51327957926.849</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>54426213572.8534</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>53168714510.3535</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>53749308582.7953</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>55620991634.2714</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>3706966.84317901</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>3691369.8373418</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>3748250.1503154</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>3840055.64308945</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>4008839.53682948</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>4304653.04305724</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>4470057.99132923</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>4367244.13224243</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>4404769.55907047</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>4540613.58345138</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>4669270.33109241</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>5025308.54639937</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>5307285.20857653</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>5421614.68131965</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>5000589.74657249</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>5337651.47911143</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>5647987.95899533</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>5847070.62080884</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>5921321.47839682</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>6195666.29667263</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>6330945.79919102</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>6546065.15447875</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>6974054.84060711</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>7000402.7445219</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>7198921.7232676</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>7451421.682381</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>7526818.33439377</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>1368157.60468325</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>1354652.74774401</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>1352565.39536997</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>1375223.85786684</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>1427225.26942683</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>1475951.62023184</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1447296.04478334</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>1488344.06795803</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>1673842.43500128</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>1534048.43455075</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>1520826.82026448</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>1571812.49410633</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>1631639.32634152</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>1649846.67240815</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>1640759.92983195</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>1691519.13776875</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>1759292.34428977</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>1790405.09129841</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>1846103.62629726</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>1922500.10321682</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>1945559.91267858</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>2001244.8288935</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2119987.9723268</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>2224220.08619445</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2224404.38257006</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>2279053.23714022</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>2283598.01827504</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
         </is>
       </c>
     </row>
@@ -3614,7 +5855,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3637,36 +5878,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3678,331 +5934,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -4039,6 +6659,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>EXI382</t>
